--- a/source/library_data.xlsx
+++ b/source/library_data.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\book_market_project\project_case_bookmarket\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1529BD-523D-40E1-9F09-2A1905BBBC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05E199A-F061-40B3-85D1-9920361A7BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="books_list" sheetId="1" r:id="rId1"/>
-    <sheet name="readers" sheetId="2" r:id="rId2"/>
-    <sheet name="book_issuance" sheetId="3" r:id="rId3"/>
-    <sheet name="book_reviews" sheetId="4" r:id="rId4"/>
-    <sheet name="genre" sheetId="5" r:id="rId5"/>
+    <sheet name="BooksList" sheetId="1" r:id="rId1"/>
+    <sheet name="Readers" sheetId="2" r:id="rId2"/>
+    <sheet name="BookIssuance" sheetId="3" r:id="rId3"/>
+    <sheet name="BookReviews" sheetId="4" r:id="rId4"/>
+    <sheet name="Genre" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -26,21 +26,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="327">
   <si>
-    <t>book_id</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>year_published</t>
-  </si>
-  <si>
-    <t>genre_id</t>
-  </si>
-  <si>
     <t>Sometimes usually into back mother</t>
   </si>
   <si>
@@ -341,18 +326,6 @@
     <t>Francisco May</t>
   </si>
   <si>
-    <t>reader_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>registered_date</t>
-  </si>
-  <si>
     <t>Wendy Herrera</t>
   </si>
   <si>
@@ -953,24 +926,6 @@
     <t>vcompton@hardy-yang.com</t>
   </si>
   <si>
-    <t>issuance_id</t>
-  </si>
-  <si>
-    <t>issue_date</t>
-  </si>
-  <si>
-    <t>return_date</t>
-  </si>
-  <si>
-    <t>review_id</t>
-  </si>
-  <si>
-    <t>rating</t>
-  </si>
-  <si>
-    <t>genre_name</t>
-  </si>
-  <si>
     <t>Fantasy</t>
   </si>
   <si>
@@ -1005,6 +960,51 @@
   </si>
   <si>
     <t>Poetry</t>
+  </si>
+  <si>
+    <t>ReaderId</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>RegisteredDate</t>
+  </si>
+  <si>
+    <t>BookId</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>YearPublished</t>
+  </si>
+  <si>
+    <t>GenreId</t>
+  </si>
+  <si>
+    <t>IssuanceId</t>
+  </si>
+  <si>
+    <t>IssueDate</t>
+  </si>
+  <si>
+    <t>ReturnDate</t>
+  </si>
+  <si>
+    <t>ReviewId</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>GenreName</t>
   </si>
 </sst>
 </file>
@@ -1388,19 +1388,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>318</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1408,10 +1408,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>1995</v>
@@ -1425,10 +1425,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D3">
         <v>1982</v>
@@ -1442,10 +1442,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>2002</v>
@@ -1459,10 +1459,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>1982</v>
@@ -1476,10 +1476,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>1970</v>
@@ -1493,10 +1493,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>1960</v>
@@ -1510,10 +1510,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D8">
         <v>1950</v>
@@ -1527,10 +1527,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>1966</v>
@@ -1544,10 +1544,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>1997</v>
@@ -1561,10 +1561,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D11">
         <v>2008</v>
@@ -1578,10 +1578,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D12">
         <v>1976</v>
@@ -1595,10 +1595,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D13">
         <v>2003</v>
@@ -1612,10 +1612,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D14">
         <v>1968</v>
@@ -1629,10 +1629,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D15">
         <v>1971</v>
@@ -1646,10 +1646,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D16">
         <v>2007</v>
@@ -1663,10 +1663,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D17">
         <v>2024</v>
@@ -1680,10 +1680,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D18">
         <v>1999</v>
@@ -1697,10 +1697,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D19">
         <v>1999</v>
@@ -1714,10 +1714,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D20">
         <v>1987</v>
@@ -1731,10 +1731,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D21">
         <v>2018</v>
@@ -1748,10 +1748,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D22">
         <v>1996</v>
@@ -1765,10 +1765,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D23">
         <v>1986</v>
@@ -1782,10 +1782,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D24">
         <v>1975</v>
@@ -1799,10 +1799,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D25">
         <v>2017</v>
@@ -1816,10 +1816,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D26">
         <v>2011</v>
@@ -1833,10 +1833,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D27">
         <v>2017</v>
@@ -1850,10 +1850,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D28">
         <v>1964</v>
@@ -1867,10 +1867,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D29">
         <v>1989</v>
@@ -1884,10 +1884,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D30">
         <v>1950</v>
@@ -1901,10 +1901,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D31">
         <v>1985</v>
@@ -1918,10 +1918,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D32">
         <v>2006</v>
@@ -1935,10 +1935,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D33">
         <v>1994</v>
@@ -1952,10 +1952,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D34">
         <v>2019</v>
@@ -1969,10 +1969,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D35">
         <v>2003</v>
@@ -1986,10 +1986,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D36">
         <v>1963</v>
@@ -2003,10 +2003,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D37">
         <v>1995</v>
@@ -2020,10 +2020,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D38">
         <v>1972</v>
@@ -2037,10 +2037,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D39">
         <v>2024</v>
@@ -2054,10 +2054,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D40">
         <v>1964</v>
@@ -2071,10 +2071,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D41">
         <v>1998</v>
@@ -2088,10 +2088,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D42">
         <v>1950</v>
@@ -2105,10 +2105,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D43">
         <v>1982</v>
@@ -2122,10 +2122,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D44">
         <v>1979</v>
@@ -2139,10 +2139,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D45">
         <v>1983</v>
@@ -2156,10 +2156,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D46">
         <v>1971</v>
@@ -2173,10 +2173,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D47">
         <v>1994</v>
@@ -2190,10 +2190,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D48">
         <v>1970</v>
@@ -2207,10 +2207,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D49">
         <v>2019</v>
@@ -2224,10 +2224,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D50">
         <v>1969</v>
@@ -2241,10 +2241,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D51">
         <v>1994</v>
@@ -2270,16 +2270,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>313</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>314</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,10 +2287,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2">
         <v>44864</v>
@@ -2301,10 +2301,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D3" s="2">
         <v>44676</v>
@@ -2315,10 +2315,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D4" s="2">
         <v>44396</v>
@@ -2329,10 +2329,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D5" s="2">
         <v>44312</v>
@@ -2343,10 +2343,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D6" s="2">
         <v>44964</v>
@@ -2357,10 +2357,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D7" s="2">
         <v>45571</v>
@@ -2371,10 +2371,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D8" s="2">
         <v>45661</v>
@@ -2385,10 +2385,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D9" s="2">
         <v>45329</v>
@@ -2399,10 +2399,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D10" s="2">
         <v>45657</v>
@@ -2413,10 +2413,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D11" s="2">
         <v>44316</v>
@@ -2427,10 +2427,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D12" s="2">
         <v>44994</v>
@@ -2441,10 +2441,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D13" s="2">
         <v>44879</v>
@@ -2455,10 +2455,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D14" s="2">
         <v>44269</v>
@@ -2469,10 +2469,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D15" s="2">
         <v>45278</v>
@@ -2483,10 +2483,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D16" s="2">
         <v>45424</v>
@@ -2497,10 +2497,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D17" s="2">
         <v>44304</v>
@@ -2511,10 +2511,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D18" s="2">
         <v>45260</v>
@@ -2525,10 +2525,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D19" s="2">
         <v>44785</v>
@@ -2539,10 +2539,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D20" s="2">
         <v>45481</v>
@@ -2553,10 +2553,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D21" s="2">
         <v>45198</v>
@@ -2567,10 +2567,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D22" s="2">
         <v>44152</v>
@@ -2581,10 +2581,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D23" s="2">
         <v>44096</v>
@@ -2595,10 +2595,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D24" s="2">
         <v>44800</v>
@@ -2609,10 +2609,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D25" s="2">
         <v>45562</v>
@@ -2623,10 +2623,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D26" s="2">
         <v>44793</v>
@@ -2637,10 +2637,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D27" s="2">
         <v>44860</v>
@@ -2651,10 +2651,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D28" s="2">
         <v>44802</v>
@@ -2665,10 +2665,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D29" s="2">
         <v>44061</v>
@@ -2679,10 +2679,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D30" s="2">
         <v>44215</v>
@@ -2693,10 +2693,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D31" s="2">
         <v>45464</v>
@@ -2707,10 +2707,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D32" s="2">
         <v>44008</v>
@@ -2721,10 +2721,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D33" s="2">
         <v>44966</v>
@@ -2735,10 +2735,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D34" s="2">
         <v>44192</v>
@@ -2749,10 +2749,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D35" s="2">
         <v>45696</v>
@@ -2763,10 +2763,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D36" s="2">
         <v>45251</v>
@@ -2777,10 +2777,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D37" s="2">
         <v>45277</v>
@@ -2791,10 +2791,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D38" s="2">
         <v>44581</v>
@@ -2805,10 +2805,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D39" s="2">
         <v>45634</v>
@@ -2819,10 +2819,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D40" s="2">
         <v>44262</v>
@@ -2833,10 +2833,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D41" s="2">
         <v>44315</v>
@@ -2847,10 +2847,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="D42" s="2">
         <v>44829</v>
@@ -2861,10 +2861,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D43" s="2">
         <v>45167</v>
@@ -2875,10 +2875,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D44" s="2">
         <v>44942</v>
@@ -2889,10 +2889,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D45" s="2">
         <v>43931</v>
@@ -2903,10 +2903,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D46" s="2">
         <v>45520</v>
@@ -2917,10 +2917,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C47" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D47" s="2">
         <v>45183</v>
@@ -2931,10 +2931,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D48" s="2">
         <v>44647</v>
@@ -2945,10 +2945,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C49" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D49" s="2">
         <v>45480</v>
@@ -2959,10 +2959,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D50" s="2">
         <v>44042</v>
@@ -2973,10 +2973,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="D51" s="2">
         <v>44443</v>
@@ -2987,10 +2987,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D52" s="2">
         <v>45007</v>
@@ -3001,10 +3001,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D53" s="2">
         <v>45698</v>
@@ -3015,10 +3015,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="D54" s="2">
         <v>44781</v>
@@ -3029,10 +3029,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D55" s="2">
         <v>45707</v>
@@ -3043,10 +3043,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D56" s="2">
         <v>45600</v>
@@ -3057,10 +3057,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C57" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D57" s="2">
         <v>44836</v>
@@ -3071,10 +3071,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D58" s="2">
         <v>44929</v>
@@ -3085,10 +3085,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D59" s="2">
         <v>44825</v>
@@ -3099,10 +3099,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="D60" s="2">
         <v>44550</v>
@@ -3113,10 +3113,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C61" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="D61" s="2">
         <v>44048</v>
@@ -3127,10 +3127,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="D62" s="2">
         <v>45557</v>
@@ -3141,10 +3141,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="D63" s="2">
         <v>45154</v>
@@ -3155,10 +3155,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C64" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D64" s="2">
         <v>44071</v>
@@ -3169,10 +3169,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C65" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D65" s="2">
         <v>45465</v>
@@ -3183,10 +3183,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D66" s="2">
         <v>45536</v>
@@ -3197,10 +3197,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C67" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D67" s="2">
         <v>45483</v>
@@ -3211,10 +3211,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C68" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D68" s="2">
         <v>44777</v>
@@ -3225,10 +3225,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C69" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D69" s="2">
         <v>44099</v>
@@ -3239,10 +3239,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C70" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D70" s="2">
         <v>44862</v>
@@ -3253,10 +3253,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C71" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D71" s="2">
         <v>44326</v>
@@ -3267,10 +3267,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D72" s="2">
         <v>44424</v>
@@ -3281,10 +3281,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="D73" s="2">
         <v>45022</v>
@@ -3295,10 +3295,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C74" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D74" s="2">
         <v>44040</v>
@@ -3309,10 +3309,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C75" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D75" s="2">
         <v>44626</v>
@@ -3323,10 +3323,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D76" s="2">
         <v>44407</v>
@@ -3337,10 +3337,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C77" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D77" s="2">
         <v>45040</v>
@@ -3351,10 +3351,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C78" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D78" s="2">
         <v>45661</v>
@@ -3365,10 +3365,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C79" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D79" s="2">
         <v>45710</v>
@@ -3379,10 +3379,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C80" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D80" s="2">
         <v>45614</v>
@@ -3393,10 +3393,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C81" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D81" s="2">
         <v>44016</v>
@@ -3407,10 +3407,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C82" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D82" s="2">
         <v>44991</v>
@@ -3421,10 +3421,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C83" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D83" s="2">
         <v>45423</v>
@@ -3435,10 +3435,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C84" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="D84" s="2">
         <v>45261</v>
@@ -3449,10 +3449,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C85" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D85" s="2">
         <v>45679</v>
@@ -3463,10 +3463,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D86" s="2">
         <v>43943</v>
@@ -3477,10 +3477,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C87" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D87" s="2">
         <v>45469</v>
@@ -3491,10 +3491,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C88" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D88" s="2">
         <v>44366</v>
@@ -3505,10 +3505,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C89" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D89" s="2">
         <v>45224</v>
@@ -3519,10 +3519,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C90" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D90" s="2">
         <v>44804</v>
@@ -3533,10 +3533,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C91" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D91" s="2">
         <v>43987</v>
@@ -3547,10 +3547,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C92" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D92" s="2">
         <v>44947</v>
@@ -3561,10 +3561,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C93" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D93" s="2">
         <v>45739</v>
@@ -3575,10 +3575,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C94" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D94" s="2">
         <v>45124</v>
@@ -3589,10 +3589,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C95" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D95" s="2">
         <v>45060</v>
@@ -3603,10 +3603,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D96" s="2">
         <v>45489</v>
@@ -3617,10 +3617,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C97" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D97" s="2">
         <v>44381</v>
@@ -3631,10 +3631,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C98" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D98" s="2">
         <v>45135</v>
@@ -3645,10 +3645,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C99" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D99" s="2">
         <v>44863</v>
@@ -3659,10 +3659,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C100" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D100" s="2">
         <v>45629</v>
@@ -3673,10 +3673,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C101" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D101" s="2">
         <v>44473</v>
@@ -3698,19 +3698,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -12225,16 +12225,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -19253,10 +19253,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>320</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -19264,7 +19264,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -19272,7 +19272,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -19280,7 +19280,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -19288,7 +19288,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -19296,7 +19296,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -19304,7 +19304,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -19312,7 +19312,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -19320,7 +19320,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -19328,7 +19328,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -19336,7 +19336,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -19344,7 +19344,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -19352,7 +19352,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
